--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\syuuj\spoon\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\syuuj\SpoonCKv2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA7E52E-6495-43BF-8868-B67235359863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464BD21A-1031-417B-8A2B-E96BB4C79451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{0D9401AE-FB63-4DA5-8A12-275353EA90A9}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="1" xr2:uid="{0D9401AE-FB63-4DA5-8A12-275353EA90A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="gitData" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="98">
   <si>
     <t>CtInvocation</t>
     <phoneticPr fontId="1"/>
@@ -663,6 +664,184 @@
     </rPh>
     <rPh sb="24" eb="26">
       <t>カイセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>checkstyle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bugのラベルはある</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>logではissue番号が表示されている　おそらく修正したコミット</t>
+    <rPh sb="10" eb="12">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コミット数</t>
+    <rPh sb="4" eb="5">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bug ラベル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CoreNLP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しかし、最新のissueになるにつれてラベルが貼られていない</t>
+    <rPh sb="4" eb="6">
+      <t>サイシン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dbeaver</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>logに修正したことが記述されているものもある</t>
+    <rPh sb="4" eb="6">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キジュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bugのラベルはある。しかし、bugのIDを得られない</t>
+    <rPh sb="22" eb="23">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>elasticsearch Analysis</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fastjson</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bugのラベルはある。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中国語で読めない</t>
+    <rPh sb="0" eb="3">
+      <t>チュウゴクゴ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>issue数</t>
+    <rPh sb="5" eb="6">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gson</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bugラベルに基づいてコメントが書かれていない</t>
+    <rPh sb="7" eb="8">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>guava</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bugはないが、type=defectがbugの代わり</t>
+    <rPh sb="24" eb="25">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>おそらく修正されたものは削除されている、logとして出力されない</t>
+    <rPh sb="4" eb="6">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hikari</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bugはない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラベル付けをしていない</t>
+    <rPh sb="3" eb="4">
+      <t>ヅ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Java-faker</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>jedis</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bugラベルに基づいてコメントが書かれている場合もある</t>
+    <rPh sb="7" eb="8">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1381,4 +1560,232 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C735ED-E794-45F2-AD08-92A43ED1D15B}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="21.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="60.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2">
+        <v>15684</v>
+      </c>
+      <c r="C2">
+        <v>693</v>
+      </c>
+      <c r="D2">
+        <v>4954</v>
+      </c>
+      <c r="E2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3">
+        <v>17416</v>
+      </c>
+      <c r="C3">
+        <v>64</v>
+      </c>
+      <c r="D3">
+        <v>953</v>
+      </c>
+      <c r="E3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4">
+        <v>27883</v>
+      </c>
+      <c r="C4">
+        <v>9244</v>
+      </c>
+      <c r="D4">
+        <v>16608</v>
+      </c>
+      <c r="E4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6">
+        <v>3983</v>
+      </c>
+      <c r="C6">
+        <v>230</v>
+      </c>
+      <c r="D6">
+        <v>1694</v>
+      </c>
+      <c r="E6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7">
+        <v>2155</v>
+      </c>
+      <c r="C7">
+        <v>156</v>
+      </c>
+      <c r="D7">
+        <v>1423</v>
+      </c>
+      <c r="E7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8">
+        <v>7121</v>
+      </c>
+      <c r="C8">
+        <v>463</v>
+      </c>
+      <c r="D8">
+        <v>3013</v>
+      </c>
+      <c r="E8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9">
+        <v>2975</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1408</v>
+      </c>
+      <c r="E9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11">
+        <v>2615</v>
+      </c>
+      <c r="C11">
+        <v>108</v>
+      </c>
+      <c r="D11">
+        <v>1842</v>
+      </c>
+      <c r="E11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\syuuj\SpoonCKv2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464BD21A-1031-417B-8A2B-E96BB4C79451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198B7791-37CC-4B04-A5C6-70B689BB8058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="1" xr2:uid="{0D9401AE-FB63-4DA5-8A12-275353EA90A9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{0D9401AE-FB63-4DA5-8A12-275353EA90A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\syuuj\SpoonCKv2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198B7791-37CC-4B04-A5C6-70B689BB8058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145E60E9-CC5C-4056-82A7-97A91B7AE9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{0D9401AE-FB63-4DA5-8A12-275353EA90A9}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="1" xr2:uid="{0D9401AE-FB63-4DA5-8A12-275353EA90A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="122">
   <si>
     <t>CtInvocation</t>
     <phoneticPr fontId="1"/>
@@ -793,19 +793,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>おそらく修正されたものは削除されている、logとして出力されない</t>
-    <rPh sb="4" eb="6">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>シュツリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Hikari</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -833,7 +820,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>bugラベルに基づいてコメントが書かれている場合もある</t>
+    <t>bugラベルに基づいてコメントが書かれている場合もある。プルリクエストにもbugラベルがついており、修正されているものはマージされている</t>
     <rPh sb="7" eb="8">
       <t>モト</t>
     </rPh>
@@ -843,6 +830,127 @@
     <rPh sb="22" eb="24">
       <t>バアイ</t>
     </rPh>
+    <rPh sb="50" eb="52">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>URLで貼られている（#111ではなく、https://github/…/issue/111)</t>
+    <rPh sb="4" eb="5">
+      <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>△</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Jenkins</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JitWatch</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Jsoup</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Junit</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Libgdx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mockserver</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mybatis</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NanoHttpd</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Netty</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Redisson</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Retrofit</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Shopizer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Vert</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Webmagic</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>YaoSerial</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Zookeeper</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プルリクエストのbugタグで判断できる</t>
+    <rPh sb="14" eb="16">
+      <t>ハンダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bugラベルはある。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紐づけられていない</t>
+    <rPh sb="0" eb="1">
+      <t>ヒモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bugラベルはある。紐づいていたりいなかったり</t>
+    <rPh sb="10" eb="11">
+      <t>ヒモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bugラベルはある。比較的紐づいている</t>
+    <rPh sb="10" eb="14">
+      <t>ヒカクテキヒモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紐づけられていたり、づけられてなかったり</t>
+    <rPh sb="0" eb="1">
+      <t>ヒモ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mapstruct</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1564,7 +1672,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C735ED-E794-45F2-AD08-92A43ED1D15B}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="21.75" bestFit="1" customWidth="1"/>
@@ -1627,7 +1735,7 @@
         <v>76</v>
       </c>
       <c r="G3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
@@ -1650,7 +1758,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
@@ -1661,7 +1769,7 @@
         <v>81</v>
       </c>
       <c r="G5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
@@ -1707,7 +1815,7 @@
         <v>87</v>
       </c>
       <c r="G7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
@@ -1727,15 +1835,15 @@
         <v>89</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B9">
         <v>2975</v>
@@ -1747,18 +1855,18 @@
         <v>1408</v>
       </c>
       <c r="E9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" t="s">
         <v>92</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>93</v>
-      </c>
-      <c r="G9" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1766,10 +1874,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B11">
-        <v>2615</v>
+        <v>2655</v>
       </c>
       <c r="C11">
         <v>108</v>
@@ -1781,7 +1889,167 @@
         <v>83</v>
       </c>
       <c r="F11" t="s">
-        <v>97</v>
+        <v>96</v>
+      </c>
+      <c r="G11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12">
+        <v>37744</v>
+      </c>
+      <c r="C12">
+        <v>6963</v>
+      </c>
+      <c r="D12">
+        <v>9194</v>
+      </c>
+      <c r="E12" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13">
+        <v>1094</v>
+      </c>
+      <c r="C13">
+        <v>61</v>
+      </c>
+      <c r="D13">
+        <v>255</v>
+      </c>
+      <c r="E13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14">
+        <v>2360</v>
+      </c>
+      <c r="C14">
+        <v>183</v>
+      </c>
+      <c r="D14">
+        <v>1579</v>
+      </c>
+      <c r="E14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15">
+        <v>2518</v>
+      </c>
+      <c r="C15">
+        <v>88</v>
+      </c>
+      <c r="D15">
+        <v>836</v>
+      </c>
+      <c r="E15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16">
+        <v>15569</v>
+      </c>
+      <c r="C16">
+        <v>371</v>
+      </c>
+      <c r="D16">
+        <v>3593</v>
+      </c>
+      <c r="E16" t="s">
+        <v>116</v>
+      </c>
+      <c r="F16" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\syuuj\SpoonCKv2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145E60E9-CC5C-4056-82A7-97A91B7AE9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415FB5EA-A6F6-4D13-8235-A936BB86C5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" activeTab="1" xr2:uid="{0D9401AE-FB63-4DA5-8A12-275353EA90A9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{0D9401AE-FB63-4DA5-8A12-275353EA90A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="124">
   <si>
     <t>CtInvocation</t>
     <phoneticPr fontId="1"/>
@@ -951,6 +951,23 @@
   </si>
   <si>
     <t>Mapstruct</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>識別子が無理</t>
+    <rPh sb="0" eb="3">
+      <t>シキベツシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ムリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重複ファイル</t>
+    <rPh sb="0" eb="2">
+      <t>チョウフク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -981,12 +998,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1003,11 +1026,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1672,16 +1698,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C735ED-E794-45F2-AD08-92A43ED1D15B}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="21.75" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="60.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
         <v>73</v>
       </c>
@@ -1692,7 +1719,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1715,7 +1742,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -1738,7 +1765,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>77</v>
       </c>
@@ -1761,7 +1788,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>80</v>
       </c>
@@ -1772,7 +1799,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -1795,7 +1822,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>86</v>
       </c>
@@ -1818,7 +1845,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>88</v>
       </c>
@@ -1840,8 +1867,11 @@
       <c r="G8" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>90</v>
       </c>
@@ -1864,7 +1894,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>94</v>
       </c>
@@ -1872,7 +1902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>95</v>
       </c>
@@ -1895,7 +1925,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>99</v>
       </c>
@@ -1917,45 +1947,48 @@
       <c r="G12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
+      <c r="H12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>1094</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>61</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>255</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
+    <row r="14" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>2360</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>183</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>1579</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>102</v>
       </c>
@@ -1972,7 +2005,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>103</v>
       </c>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\syuuj\SpoonCKv2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sugii syuji\SpoonCKv2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415FB5EA-A6F6-4D13-8235-A936BB86C5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCEAEBE-1CF5-4F1B-B342-72E623C8ECAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{0D9401AE-FB63-4DA5-8A12-275353EA90A9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{0D9401AE-FB63-4DA5-8A12-275353EA90A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="129">
   <si>
     <t>CtInvocation</t>
     <phoneticPr fontId="1"/>
@@ -704,16 +704,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>しかし、最新のissueになるにつれてラベルが貼られていない</t>
-    <rPh sb="4" eb="6">
-      <t>サイシン</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ハ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Dbeaver</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -728,13 +718,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>bugのラベルはある。しかし、bugのIDを得られない</t>
-    <rPh sb="22" eb="23">
-      <t>エ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>elasticsearch Analysis</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -797,17 +780,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>bugはない</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ラベル付けをしていない</t>
-    <rPh sb="3" eb="4">
-      <t>ヅ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>×</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -968,6 +940,90 @@
     <rPh sb="0" eb="2">
       <t>チョウフク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しかし、最新のissueになるにつれてラベルが貼られていない(2019以降)</t>
+    <rPh sb="4" eb="6">
+      <t>サイシン</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bugのラベルはある。しかし、typeにbugが設定されており入手不可</t>
+    <rPh sb="24" eb="26">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ニュウシュ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bugのラベルはある。2022年12月以降bugラベルがない</t>
+    <rPh sb="15" eb="16">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fix issue #111</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fixes [URL]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bugラベルはある．2024年9月以降bugラベルはない</t>
+    <rPh sb="14" eb="15">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラベル付けされている</t>
+    <rPh sb="3" eb="4">
+      <t>ヅ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bugラベルはある。しかし，typeにbugが設定されており入手不可</t>
+    <rPh sb="23" eb="25">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ニュウシュ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Fixes #111</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1371,16 +1427,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67CE49E5-5A0E-41D6-BDF6-D0FD09293F4B}">
   <dimension ref="A2:H57"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="78" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="66.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="67.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.58203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="66.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="67.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1391,7 +1447,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1402,17 +1458,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="C5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1423,17 +1479,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="C8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="C9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1441,7 +1497,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1449,12 +1505,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="C15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="C17" t="s">
         <v>16</v>
       </c>
@@ -1465,7 +1521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="C18" t="s">
         <v>18</v>
       </c>
@@ -1473,47 +1529,47 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="C19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="C20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="C21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="C23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="C24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="C25" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="C26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="C27" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1524,7 +1580,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1535,7 +1591,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1546,7 +1602,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -1554,7 +1610,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -1568,7 +1624,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -1588,7 +1644,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="E35" t="s">
         <v>44</v>
       </c>
@@ -1596,7 +1652,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -1613,7 +1669,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="C37" t="s">
         <v>56</v>
       </c>
@@ -1621,7 +1677,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>0</v>
       </c>
@@ -1629,17 +1685,17 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="C39" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="C40" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>32</v>
       </c>
@@ -1647,22 +1703,22 @@
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="C46" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="C47" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="C49" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>64</v>
       </c>
@@ -1670,22 +1726,22 @@
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="C53" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="C55" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="C56" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="C57" t="s">
         <v>69</v>
       </c>
@@ -1698,17 +1754,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C735ED-E794-45F2-AD08-92A43ED1D15B}">
-  <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="21.75" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="60.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="128.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" t="s">
         <v>73</v>
       </c>
@@ -1716,10 +1774,10 @@
         <v>74</v>
       </c>
       <c r="D1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1739,10 +1797,13 @@
         <v>72</v>
       </c>
       <c r="G2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -1759,15 +1820,15 @@
         <v>71</v>
       </c>
       <c r="F3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
         <v>76</v>
-      </c>
-      <c r="G3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>77</v>
       </c>
       <c r="B4">
         <v>27883</v>
@@ -1779,29 +1840,29 @@
         <v>16608</v>
       </c>
       <c r="E4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
         <v>79</v>
       </c>
-      <c r="F4" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+      <c r="H5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
         <v>80</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>82</v>
       </c>
       <c r="B6">
         <v>3983</v>
@@ -1813,18 +1874,21 @@
         <v>1694</v>
       </c>
       <c r="E6" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="F6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
         <v>84</v>
-      </c>
-      <c r="G6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>86</v>
       </c>
       <c r="B7">
         <v>2155</v>
@@ -1839,15 +1903,15 @@
         <v>71</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+        <v>85</v>
+      </c>
+      <c r="H7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B8">
         <v>7121</v>
@@ -1859,21 +1923,24 @@
         <v>3013</v>
       </c>
       <c r="E8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G8" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="H8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+        <v>94</v>
+      </c>
+      <c r="I8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B9">
         <v>2975</v>
@@ -1885,26 +1952,26 @@
         <v>1408</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="F9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+        <v>126</v>
+      </c>
+      <c r="H9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B11">
         <v>2655</v>
@@ -1916,18 +1983,18 @@
         <v>1842</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B12">
         <v>37744</v>
@@ -1939,21 +2006,21 @@
         <v>9194</v>
       </c>
       <c r="E12" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="F12" t="s">
-        <v>115</v>
-      </c>
-      <c r="G12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" t="s">
         <v>48</v>
       </c>
-      <c r="H12" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="I12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B13" s="2">
         <v>1094</v>
@@ -1965,15 +2032,15 @@
         <v>255</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.4">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B14" s="2">
         <v>2360</v>
@@ -1985,12 +2052,15 @@
         <v>1579</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+        <v>114</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B15">
         <v>2518</v>
@@ -2002,12 +2072,12 @@
         <v>836</v>
       </c>
       <c r="E15" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B16">
         <v>15569</v>
@@ -2019,70 +2089,70 @@
         <v>3593</v>
       </c>
       <c r="E16" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16" t="s">
         <v>116</v>
       </c>
-      <c r="F16" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sugii syuji\SpoonCKv2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\syuuj\SpoonCKv2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCEAEBE-1CF5-4F1B-B342-72E623C8ECAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{84807BC2-B879-470F-9E0D-BCA717CB519E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{0D9401AE-FB63-4DA5-8A12-275353EA90A9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{0D9401AE-FB63-4DA5-8A12-275353EA90A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="gitData" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="153">
   <si>
     <t>CtInvocation</t>
     <phoneticPr fontId="1"/>
@@ -1024,6 +1025,108 @@
   </si>
   <si>
     <t>Fixes #111</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0/1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>166/184</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>348/432</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0/72</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>109(+6)/139</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紐づいてる割合(#issue(+url)/issue)</t>
+    <rPh sb="0" eb="1">
+      <t>ヒモ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ワリアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0(+0)/34</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0(+0)/1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>906(+4)/1001</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0(+0)/28</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0(+1)/13</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>248(+7)/570</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44(+0)/67</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0(+0)/2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>667/695</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>57/109</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>21(+2)/61</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>153(+1)/222</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9(+2)/157</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10(+2)/51</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6(+1)/62</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42(+1)/89</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>87(+1)/373</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0/1 (93/469)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1054,18 +1157,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1089,8 +1186,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1427,16 +1524,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67CE49E5-5A0E-41D6-BDF6-D0FD09293F4B}">
   <dimension ref="A2:H57"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="78" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.58203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="66.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="67.08203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="66.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="67.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1447,7 +1544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1458,17 +1555,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1479,17 +1576,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1497,7 +1594,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1505,12 +1602,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C17" t="s">
         <v>16</v>
       </c>
@@ -1521,7 +1618,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C18" t="s">
         <v>18</v>
       </c>
@@ -1529,47 +1626,47 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C25" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C27" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1580,7 +1677,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1591,7 +1688,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1602,7 +1699,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -1610,7 +1707,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -1624,7 +1721,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -1644,7 +1741,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="E35" t="s">
         <v>44</v>
       </c>
@@ -1652,7 +1749,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -1669,7 +1766,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="C37" t="s">
         <v>56</v>
       </c>
@@ -1677,7 +1774,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>0</v>
       </c>
@@ -1685,17 +1782,17 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="C39" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="C40" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>32</v>
       </c>
@@ -1703,22 +1800,22 @@
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="C46" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="C47" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C49" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>64</v>
       </c>
@@ -1726,22 +1823,22 @@
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C53" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C55" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C56" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C57" t="s">
         <v>69</v>
       </c>
@@ -1754,19 +1851,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C735ED-E794-45F2-AD08-92A43ED1D15B}">
-  <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="21.75" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="60.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="128.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="136" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
         <v>73</v>
       </c>
@@ -1776,8 +1873,11 @@
       <c r="D1" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="E1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1790,20 +1890,23 @@
       <c r="D2">
         <v>4954</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F2" t="s">
         <v>71</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>72</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>123</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -1816,17 +1919,20 @@
       <c r="D3">
         <v>953</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F3" t="s">
         <v>71</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>120</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>76</v>
       </c>
@@ -1839,28 +1945,32 @@
       <c r="D4">
         <v>16608</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" t="s">
         <v>121</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>77</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>78</v>
       </c>
       <c r="C5" t="s">
         <v>79</v>
       </c>
-      <c r="H5" t="s">
+      <c r="E5" s="2"/>
+      <c r="I5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>80</v>
       </c>
@@ -1873,20 +1983,23 @@
       <c r="D6">
         <v>1694</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" t="s">
         <v>122</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>82</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>123</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -1899,17 +2012,20 @@
       <c r="D7">
         <v>1423</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" t="s">
         <v>71</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>85</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>86</v>
       </c>
@@ -1922,23 +2038,26 @@
       <c r="D8">
         <v>3013</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F8" t="s">
         <v>87</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>93</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>124</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>94</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>88</v>
       </c>
@@ -1951,25 +2070,29 @@
       <c r="D9">
         <v>1408</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F9" t="s">
         <v>125</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>126</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>90</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>91</v>
       </c>
@@ -1982,17 +2105,20 @@
       <c r="D11">
         <v>1842</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F11" t="s">
         <v>81</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>92</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>95</v>
       </c>
@@ -2005,60 +2131,69 @@
       <c r="D12">
         <v>9194</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12" t="s">
         <v>127</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>111</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>48</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13">
         <v>1094</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13">
         <v>61</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13">
         <v>255</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F13" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14">
         <v>2360</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14">
         <v>183</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14">
         <v>1579</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F14" t="s">
         <v>114</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>98</v>
       </c>
@@ -2071,11 +2206,14 @@
       <c r="D15">
         <v>836</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F15" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>99</v>
       </c>
@@ -2088,71 +2226,110 @@
       <c r="D16">
         <v>3593</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F16" t="s">
         <v>112</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E17" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E18" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E19" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E20" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E21" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E22" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E23" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E24" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E25" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E26" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E27" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>110</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
